--- a/docs/files/rocscience/vp096.xlsx
+++ b/docs/files/rocscience/vp096.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/njones/python_projects/xslope/docs/inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D53F4FFA-A72E-9849-8C3B-3C3A51EB7D83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6571542-1A3D-6A42-AC36-061894174704}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11520" yWindow="2900" windowWidth="42700" windowHeight="22800" xr2:uid="{BA54C293-CE08-6E4C-9212-B3317DAA148E}"/>
   </bookViews>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="217">
   <si>
     <t>X</t>
   </si>
@@ -863,6 +863,21 @@
   </si>
   <si>
     <t>Angle</t>
+  </si>
+  <si>
+    <t>Type:</t>
+  </si>
+  <si>
+    <t>Type optons</t>
+  </si>
+  <si>
+    <t>phreatic</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Phreatic surface: static head reduced by cos² of the line's slope.</t>
+  </si>
+  <si>
+    <t>True piezometric line: u = γw × vertical distance below the line (static head).</t>
   </si>
 </sst>
 </file>
@@ -1338,13 +1353,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="16" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2560,7 +2575,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>piezo!$A$4:$A$18</c:f>
+              <c:f>piezo!$A$5:$A$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
@@ -2569,7 +2584,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>piezo!$B$4:$B$18</c:f>
+              <c:f>piezo!$B$5:$B$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
@@ -2621,7 +2636,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>piezo!$D$4:$D$18</c:f>
+              <c:f>piezo!$D$5:$D$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
@@ -2630,7 +2645,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>piezo!$E$4:$E$18</c:f>
+              <c:f>piezo!$E$5:$E$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
@@ -10335,7 +10350,7 @@
         <v>79</v>
       </c>
       <c r="D5" s="35">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
@@ -13427,10 +13442,10 @@
         <v>0.0</v>
       </c>
       <c r="AF10" s="3">
-        <v>0.0</v>
+        <v>100000.0</v>
       </c>
       <c r="AG10" s="3">
-        <v>0.0</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.2">
@@ -14484,76 +14499,76 @@
       </c>
     </row>
     <row r="4" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A4" s="53" t="inlineStr">
+      <c r="A4" s="55" t="inlineStr">
         <is>
           <t>Profile Line #1</t>
         </is>
       </c>
-      <c r="B4" s="53"/>
-      <c r="D4" s="53" t="s">
+      <c r="B4" s="55"/>
+      <c r="D4" s="55" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="53"/>
-      <c r="G4" s="53" t="s">
+      <c r="E4" s="55"/>
+      <c r="G4" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="53"/>
-      <c r="J4" s="53" t="s">
+      <c r="H4" s="55"/>
+      <c r="J4" s="55" t="s">
         <v>7</v>
       </c>
-      <c r="K4" s="53"/>
-      <c r="M4" s="53" t="s">
+      <c r="K4" s="55"/>
+      <c r="M4" s="55" t="s">
         <v>8</v>
       </c>
-      <c r="N4" s="53"/>
-      <c r="P4" s="53" t="s">
+      <c r="N4" s="55"/>
+      <c r="P4" s="55" t="s">
         <v>9</v>
       </c>
-      <c r="Q4" s="53"/>
+      <c r="Q4" s="55"/>
       <c r="R4" s="1"/>
-      <c r="S4" s="53" t="s">
+      <c r="S4" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="T4" s="53"/>
+      <c r="T4" s="55"/>
       <c r="U4" s="1"/>
-      <c r="V4" s="53" t="s">
+      <c r="V4" s="55" t="s">
         <v>11</v>
       </c>
-      <c r="W4" s="53"/>
+      <c r="W4" s="55"/>
       <c r="X4" s="1"/>
-      <c r="Y4" s="53" t="s">
+      <c r="Y4" s="55" t="s">
         <v>12</v>
       </c>
-      <c r="Z4" s="53"/>
+      <c r="Z4" s="55"/>
       <c r="AA4" s="1"/>
-      <c r="AB4" s="53" t="s">
+      <c r="AB4" s="55" t="s">
         <v>13</v>
       </c>
-      <c r="AC4" s="53"/>
-      <c r="AE4" s="53" t="s">
+      <c r="AC4" s="55"/>
+      <c r="AE4" s="55" t="s">
         <v>111</v>
       </c>
-      <c r="AF4" s="53"/>
+      <c r="AF4" s="55"/>
       <c r="AG4" s="1"/>
-      <c r="AH4" s="53" t="s">
+      <c r="AH4" s="55" t="s">
         <v>112</v>
       </c>
-      <c r="AI4" s="53"/>
+      <c r="AI4" s="55"/>
       <c r="AJ4" s="1"/>
-      <c r="AK4" s="53" t="s">
+      <c r="AK4" s="55" t="s">
         <v>113</v>
       </c>
-      <c r="AL4" s="53"/>
+      <c r="AL4" s="55"/>
       <c r="AM4" s="1"/>
-      <c r="AN4" s="53" t="s">
+      <c r="AN4" s="55" t="s">
         <v>114</v>
       </c>
-      <c r="AO4" s="53"/>
+      <c r="AO4" s="55"/>
       <c r="AP4" s="1"/>
-      <c r="AQ4" s="53" t="s">
+      <c r="AQ4" s="55" t="s">
         <v>115</v>
       </c>
-      <c r="AR4" s="53"/>
+      <c r="AR4" s="55"/>
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A5" s="41" t="s">
@@ -14656,89 +14671,89 @@
       </c>
     </row>
     <row r="6" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A6" s="54" t="str">
+      <c r="A6" s="53" t="str">
         <f>_xlfn.XLOOKUP(B5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="B6" s="55"/>
-      <c r="D6" s="54" t="str">
+      <c r="B6" s="54"/>
+      <c r="D6" s="53" t="str">
         <f>_xlfn.XLOOKUP(E5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="E6" s="55"/>
-      <c r="G6" s="54" t="str">
+      <c r="E6" s="54"/>
+      <c r="G6" s="53" t="str">
         <f>_xlfn.XLOOKUP(H5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="H6" s="55"/>
-      <c r="J6" s="54" t="str">
+      <c r="H6" s="54"/>
+      <c r="J6" s="53" t="str">
         <f>_xlfn.XLOOKUP(K5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="K6" s="55"/>
-      <c r="M6" s="54" t="str">
+      <c r="K6" s="54"/>
+      <c r="M6" s="53" t="str">
         <f>_xlfn.XLOOKUP(N5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="N6" s="55"/>
-      <c r="P6" s="54" t="str">
+      <c r="N6" s="54"/>
+      <c r="P6" s="53" t="str">
         <f>_xlfn.XLOOKUP(Q5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="Q6" s="55"/>
+      <c r="Q6" s="54"/>
       <c r="R6" s="1"/>
-      <c r="S6" s="54" t="str">
+      <c r="S6" s="53" t="str">
         <f>_xlfn.XLOOKUP(T5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="T6" s="55"/>
+      <c r="T6" s="54"/>
       <c r="U6" s="1"/>
-      <c r="V6" s="54" t="str">
+      <c r="V6" s="53" t="str">
         <f>_xlfn.XLOOKUP(W5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="W6" s="55"/>
+      <c r="W6" s="54"/>
       <c r="X6" s="1"/>
-      <c r="Y6" s="54" t="str">
+      <c r="Y6" s="53" t="str">
         <f>_xlfn.XLOOKUP(Z5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="Z6" s="55"/>
+      <c r="Z6" s="54"/>
       <c r="AA6" s="1"/>
-      <c r="AB6" s="54" t="str">
+      <c r="AB6" s="53" t="str">
         <f>_xlfn.XLOOKUP(AC5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AC6" s="55"/>
-      <c r="AE6" s="54" t="str">
+      <c r="AC6" s="54"/>
+      <c r="AE6" s="53" t="str">
         <f>_xlfn.XLOOKUP(AF5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AF6" s="55"/>
+      <c r="AF6" s="54"/>
       <c r="AG6" s="1"/>
-      <c r="AH6" s="54" t="str">
+      <c r="AH6" s="53" t="str">
         <f>_xlfn.XLOOKUP(AI5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AI6" s="55"/>
+      <c r="AI6" s="54"/>
       <c r="AJ6" s="1"/>
-      <c r="AK6" s="54" t="str">
+      <c r="AK6" s="53" t="str">
         <f>_xlfn.XLOOKUP(AL5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AL6" s="55"/>
+      <c r="AL6" s="54"/>
       <c r="AM6" s="1"/>
-      <c r="AN6" s="54" t="str">
+      <c r="AN6" s="53" t="str">
         <f>_xlfn.XLOOKUP(AO5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AO6" s="55"/>
+      <c r="AO6" s="54"/>
       <c r="AP6" s="1"/>
-      <c r="AQ6" s="54" t="str">
+      <c r="AQ6" s="53" t="str">
         <f>_xlfn.XLOOKUP(AR5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AR6" s="55"/>
+      <c r="AR6" s="54"/>
     </row>
     <row r="7" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
@@ -15658,36 +15673,36 @@
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="S4:T4"/>
+    <mergeCell ref="V4:W4"/>
+    <mergeCell ref="Y4:Z4"/>
+    <mergeCell ref="AB4:AC4"/>
+    <mergeCell ref="AE4:AF4"/>
+    <mergeCell ref="AH4:AI4"/>
+    <mergeCell ref="AK4:AL4"/>
+    <mergeCell ref="AN4:AO4"/>
+    <mergeCell ref="AQ4:AR4"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="S6:T6"/>
+    <mergeCell ref="V6:W6"/>
+    <mergeCell ref="Y6:Z6"/>
+    <mergeCell ref="AB6:AC6"/>
     <mergeCell ref="AE6:AF6"/>
     <mergeCell ref="AH6:AI6"/>
     <mergeCell ref="AK6:AL6"/>
     <mergeCell ref="AN6:AO6"/>
     <mergeCell ref="AQ6:AR6"/>
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="S6:T6"/>
-    <mergeCell ref="V6:W6"/>
-    <mergeCell ref="Y6:Z6"/>
-    <mergeCell ref="AB6:AC6"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="AE4:AF4"/>
-    <mergeCell ref="AH4:AI4"/>
-    <mergeCell ref="AK4:AL4"/>
-    <mergeCell ref="AN4:AO4"/>
-    <mergeCell ref="AQ4:AR4"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="S4:T4"/>
-    <mergeCell ref="V4:W4"/>
-    <mergeCell ref="Y4:Z4"/>
-    <mergeCell ref="AB4:AC4"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="M4:N4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -15725,74 +15740,74 @@
       </c>
     </row>
     <row r="4" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A4" s="53" t="s">
+      <c r="A4" s="55" t="s">
         <v>150</v>
       </c>
-      <c r="B4" s="53"/>
-      <c r="D4" s="53" t="s">
+      <c r="B4" s="55"/>
+      <c r="D4" s="55" t="s">
         <v>151</v>
       </c>
-      <c r="E4" s="53"/>
-      <c r="G4" s="53" t="s">
+      <c r="E4" s="55"/>
+      <c r="G4" s="55" t="s">
         <v>152</v>
       </c>
-      <c r="H4" s="53"/>
-      <c r="J4" s="53" t="s">
+      <c r="H4" s="55"/>
+      <c r="J4" s="55" t="s">
         <v>153</v>
       </c>
-      <c r="K4" s="53"/>
-      <c r="M4" s="53" t="s">
+      <c r="K4" s="55"/>
+      <c r="M4" s="55" t="s">
         <v>154</v>
       </c>
-      <c r="N4" s="53"/>
-      <c r="P4" s="53" t="s">
+      <c r="N4" s="55"/>
+      <c r="P4" s="55" t="s">
         <v>155</v>
       </c>
-      <c r="Q4" s="53"/>
+      <c r="Q4" s="55"/>
       <c r="R4" s="1"/>
-      <c r="S4" s="53" t="s">
+      <c r="S4" s="55" t="s">
         <v>156</v>
       </c>
-      <c r="T4" s="53"/>
+      <c r="T4" s="55"/>
       <c r="U4" s="1"/>
-      <c r="V4" s="53" t="s">
+      <c r="V4" s="55" t="s">
         <v>157</v>
       </c>
-      <c r="W4" s="53"/>
+      <c r="W4" s="55"/>
       <c r="X4" s="1"/>
-      <c r="Y4" s="53" t="s">
+      <c r="Y4" s="55" t="s">
         <v>158</v>
       </c>
-      <c r="Z4" s="53"/>
+      <c r="Z4" s="55"/>
       <c r="AA4" s="1"/>
-      <c r="AB4" s="53" t="s">
+      <c r="AB4" s="55" t="s">
         <v>159</v>
       </c>
-      <c r="AC4" s="53"/>
-      <c r="AE4" s="53" t="s">
+      <c r="AC4" s="55"/>
+      <c r="AE4" s="55" t="s">
         <v>160</v>
       </c>
-      <c r="AF4" s="53"/>
+      <c r="AF4" s="55"/>
       <c r="AG4" s="1"/>
-      <c r="AH4" s="53" t="s">
+      <c r="AH4" s="55" t="s">
         <v>161</v>
       </c>
-      <c r="AI4" s="53"/>
+      <c r="AI4" s="55"/>
       <c r="AJ4" s="1"/>
-      <c r="AK4" s="53" t="s">
+      <c r="AK4" s="55" t="s">
         <v>162</v>
       </c>
-      <c r="AL4" s="53"/>
+      <c r="AL4" s="55"/>
       <c r="AM4" s="1"/>
-      <c r="AN4" s="53" t="s">
+      <c r="AN4" s="55" t="s">
         <v>163</v>
       </c>
-      <c r="AO4" s="53"/>
+      <c r="AO4" s="55"/>
       <c r="AP4" s="1"/>
-      <c r="AQ4" s="53" t="s">
+      <c r="AQ4" s="55" t="s">
         <v>164</v>
       </c>
-      <c r="AR4" s="53"/>
+      <c r="AR4" s="55"/>
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A5" s="43" t="s">
@@ -16881,14 +16896,12 @@
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="AN6:AO6"/>
-    <mergeCell ref="AQ6:AR6"/>
-    <mergeCell ref="V6:W6"/>
-    <mergeCell ref="Y6:Z6"/>
-    <mergeCell ref="AB6:AC6"/>
-    <mergeCell ref="AE6:AF6"/>
-    <mergeCell ref="AH6:AI6"/>
-    <mergeCell ref="AK6:AL6"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="M4:N4"/>
     <mergeCell ref="AK4:AL4"/>
     <mergeCell ref="AN4:AO4"/>
     <mergeCell ref="AQ4:AR4"/>
@@ -16905,12 +16918,14 @@
     <mergeCell ref="AB4:AC4"/>
     <mergeCell ref="AE4:AF4"/>
     <mergeCell ref="AH4:AI4"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="AN6:AO6"/>
+    <mergeCell ref="AQ6:AR6"/>
+    <mergeCell ref="V6:W6"/>
+    <mergeCell ref="Y6:Z6"/>
+    <mergeCell ref="AB6:AC6"/>
+    <mergeCell ref="AE6:AF6"/>
+    <mergeCell ref="AH6:AI6"/>
+    <mergeCell ref="AK6:AL6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -16918,14 +16933,14 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7E1F343-68A5-3340-AF23-43D8E7E1F914}">
-  <dimension ref="A2:G23"/>
+  <dimension ref="A2:H24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="7" customWidth="1"/>
     <col min="6" max="6" width="5.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="58" t="s">
         <v>84</v>
       </c>
@@ -16938,109 +16953,138 @@
         <v>83</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3" s="37" t="s">
+        <v>212</v>
+      </c>
+      <c r="B3" s="38" t="inlineStr">
+        <is>
+          <t>piezo</t>
+        </is>
+      </c>
+      <c r="D3" s="39" t="s">
+        <v>212</v>
+      </c>
+      <c r="E3" s="40" t="inlineStr">
+        <is>
+          <t>piezo</t>
+        </is>
+      </c>
+      <c r="G3" s="24"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4" s="3">
+      <c r="G4" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="H4" s="1"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5" s="3">
         <v>0.0</v>
-      </c>
-      <c r="B4" s="3">
-        <v>103.0</v>
-      </c>
-      <c r="D4" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="E4" s="3">
-        <v>24.0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" s="3">
-        <v>380.0</v>
       </c>
       <c r="B5" s="3">
         <v>103.0</v>
       </c>
       <c r="D5" s="3">
-        <v>380.0</v>
+        <v>0.0</v>
       </c>
       <c r="E5" s="3">
         <v>24.0</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H5" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6" s="3">
+        <v>380.0</v>
+      </c>
+      <c r="B6" s="3">
+        <v>103.0</v>
+      </c>
+      <c r="D6" s="3">
+        <v>380.0</v>
+      </c>
+      <c r="E6" s="3">
+        <v>24.0</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="H6" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="3"/>
       <c r="B9" s="3"/>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A12" s="4"/>
-      <c r="B12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A12" s="3"/>
+      <c r="B12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="4"/>
       <c r="B13" s="4"/>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="4"/>
       <c r="B14" s="4"/>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="4"/>
       <c r="B15" s="4"/>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="4"/>
       <c r="B16" s="4"/>
       <c r="D16" s="4"/>
@@ -17088,11 +17132,22 @@
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
     </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A24" s="4"/>
+      <c r="B24" s="4"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="D2:E2"/>
   </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3 E3" xr:uid="{62365587-5741-D749-B74F-CDA32F05212C}">
+      <formula1>$G$5:$G$6</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
